--- a/data/batches/B07_Findings_value_mismatch/Test_Validation_Report/Test_Validation_Report_B07.xlsx
+++ b/data/batches/B07_Findings_value_mismatch/Test_Validation_Report/Test_Validation_Report_B07.xlsx
@@ -5004,11 +5004,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0019</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -5035,11 +5031,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5062,7 +5054,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -5087,11 +5079,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0019</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -5118,11 +5106,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5145,7 +5129,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -5170,11 +5154,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0019</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -5201,11 +5181,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5228,7 +5204,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -5253,11 +5229,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0015</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -5284,11 +5256,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5311,7 +5279,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -5336,11 +5304,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>BI-1245.110-BRA_SITE01-0010</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -5367,11 +5331,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5394,7 +5354,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -5419,11 +5379,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>BI-1245.110-POL_SITE01-0006</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -5450,11 +5406,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5477,7 +5429,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -5502,11 +5454,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0016</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -5533,11 +5481,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5560,7 +5504,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -5585,11 +5529,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0013</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -5616,11 +5556,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5643,7 +5579,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -5668,11 +5604,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0005</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -5699,11 +5631,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5726,7 +5654,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -5751,11 +5679,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE02-0014</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -5782,11 +5706,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5809,7 +5729,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -5834,11 +5754,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0008</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -5865,11 +5781,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5892,7 +5804,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -5917,11 +5829,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>BI-1245.110-BRA_SITE01-0020</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -5948,11 +5856,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5975,7 +5879,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6000,11 +5904,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE02-0014</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -6031,11 +5931,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6058,7 +5954,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6083,11 +5979,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>BI-1245.110-BRA_SITE01-0010</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -6114,11 +6006,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6141,7 +6029,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6166,11 +6054,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>BI-1245.110-POL_SITE01-0006</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -6197,11 +6081,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6224,7 +6104,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6249,11 +6129,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE02-0014</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -6280,11 +6156,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6307,7 +6179,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6332,11 +6204,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE02-0014</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -6363,11 +6231,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6390,7 +6254,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6415,11 +6279,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0008</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -6446,11 +6306,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6473,7 +6329,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6498,11 +6354,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE02-0014</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -6529,11 +6381,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6556,7 +6404,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6581,11 +6429,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>BI-1245.110-POL_SITE01-0006</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -6612,11 +6456,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6639,7 +6479,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6664,11 +6504,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0019</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -6695,11 +6531,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6722,7 +6554,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6747,11 +6579,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE02-0014</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -6778,11 +6606,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6805,7 +6629,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6830,11 +6654,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>BI-1245.110-ARG_SITE01-0017</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -6861,11 +6681,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6888,7 +6704,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6913,11 +6729,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>BI-1245.110-BRA_SITE01-0020</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -6944,11 +6756,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6971,7 +6779,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6996,11 +6804,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>BI-1245.110-ARG_SITE01-0017</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -7027,11 +6831,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7054,7 +6854,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7079,11 +6879,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0003</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -7110,11 +6906,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7137,7 +6929,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7162,11 +6954,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>BI-1245.110-POL_SITE01-0006</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -7193,11 +6981,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7220,7 +7004,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7245,11 +7029,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>BI-1245.110-BRA_SITE01-0020</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -7276,11 +7056,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7303,7 +7079,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7328,11 +7104,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE02-0014</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -7359,11 +7131,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7386,7 +7154,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7411,11 +7179,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>BI-1245.110-POL_SITE01-0006</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -7442,11 +7206,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7469,7 +7229,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7494,11 +7254,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>BI-1245.110-POL_SITE01-0006</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -7525,11 +7281,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7552,7 +7304,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7577,11 +7329,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>BI-1245.110-ARG_SITE01-0017</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -7608,11 +7356,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7635,7 +7379,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7660,11 +7404,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0016</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -7691,11 +7431,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7718,7 +7454,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7743,11 +7479,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0015</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -7774,11 +7506,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7801,7 +7529,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7826,11 +7554,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE02-0014</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -7857,11 +7581,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7884,7 +7604,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7909,11 +7629,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>BI-1245.110-POL_SITE01-0006</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -7940,11 +7656,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7967,7 +7679,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7992,11 +7704,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0003</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -8023,11 +7731,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8050,7 +7754,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8075,11 +7779,7 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>BI-1245.110-ARG_SITE01-0017</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>DASTRESU</t>
@@ -8106,11 +7806,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8133,7 +7829,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8158,11 +7854,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0018</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -8189,11 +7881,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8216,7 +7904,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8241,11 +7929,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0013</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -8272,11 +7956,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>beats/min</t>
-        </is>
-      </c>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8299,7 +7979,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8324,11 +8004,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0018</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -8355,11 +8031,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8382,7 +8054,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8407,11 +8079,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0015</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -8438,11 +8106,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8465,7 +8129,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8490,11 +8154,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0015</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -8521,11 +8181,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8548,7 +8204,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8573,11 +8229,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0005</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -8604,11 +8256,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8631,7 +8279,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8656,11 +8304,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0003</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -8687,11 +8331,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8714,7 +8354,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8739,11 +8379,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0015</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -8770,11 +8406,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8797,7 +8429,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8822,11 +8454,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE02-0002</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -8853,11 +8481,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>beats/min</t>
-        </is>
-      </c>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8880,7 +8504,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8905,11 +8529,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0015</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -8936,11 +8556,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8963,7 +8579,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8988,11 +8604,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0013</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -9019,11 +8631,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9046,7 +8654,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -9071,11 +8679,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0013</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -9102,11 +8706,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9129,7 +8729,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -9154,11 +8754,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0003</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -9185,11 +8781,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9212,7 +8804,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -9237,11 +8829,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0016</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -9268,11 +8856,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9295,7 +8879,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -9320,11 +8904,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0003</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -9351,11 +8931,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>beats/min</t>
-        </is>
-      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9378,7 +8954,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -9403,11 +8979,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0008</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>EGSTRESU</t>
@@ -9434,11 +9006,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9461,7 +9029,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -9486,11 +9054,7 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0016</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>LBSTRESU</t>
@@ -9517,11 +9081,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>U/L</t>
-        </is>
-      </c>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9544,7 +9104,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -9569,11 +9129,7 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0016</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>LBSTRESU</t>
@@ -9600,11 +9156,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>10^9/L</t>
-        </is>
-      </c>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9627,7 +9179,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -9652,11 +9204,7 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0005</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>LBSTRESU</t>
@@ -9683,11 +9231,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>U/L</t>
-        </is>
-      </c>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9710,7 +9254,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -9735,11 +9279,7 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0018</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>LBSTRESU</t>
@@ -9766,11 +9306,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>10^9/L</t>
-        </is>
-      </c>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9793,7 +9329,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -9818,11 +9354,7 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0016</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>LBSTRESU</t>
@@ -9849,11 +9381,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>10^9/L</t>
-        </is>
-      </c>
+      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9876,7 +9404,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -9901,11 +9429,7 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0005</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>LBSTRESU</t>
@@ -9932,11 +9456,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>U/L</t>
-        </is>
-      </c>
+      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9959,7 +9479,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -9984,11 +9504,7 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0016</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>LBSTRESU</t>
@@ -10015,11 +9531,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>mmol/L</t>
-        </is>
-      </c>
+      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10042,7 +9554,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -10067,11 +9579,7 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0005</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>LBSTRESU</t>
@@ -10098,11 +9606,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>mmol/L</t>
-        </is>
-      </c>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10125,7 +9629,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -10150,11 +9654,7 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0016</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>LBSTRESU</t>
@@ -10181,11 +9681,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>umol/L</t>
-        </is>
-      </c>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10208,7 +9704,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -10233,11 +9729,7 @@
           <t>PC</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0008</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>PCSTRESU</t>
@@ -10264,11 +9756,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>ng/mL</t>
-        </is>
-      </c>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10291,7 +9779,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -10316,11 +9804,7 @@
           <t>PC</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0008</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>PCSTRESU</t>
@@ -10347,11 +9831,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>ng/mL</t>
-        </is>
-      </c>
+      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10374,7 +9854,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -10399,11 +9879,7 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE02-0002</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>PPSTRESU</t>
@@ -10430,11 +9906,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>h*ng/mL</t>
-        </is>
-      </c>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10457,7 +9929,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -10482,11 +9954,7 @@
           <t>VS</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE02-0002</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>VSSTRESU</t>
@@ -10513,11 +9981,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10540,7 +10004,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -10565,11 +10029,7 @@
           <t>VS</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE02-0002</t>
-        </is>
-      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>VSSTRESU</t>
@@ -10596,11 +10056,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10623,7 +10079,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -10648,11 +10104,7 @@
           <t>VS</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0018</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>VSSTRESU</t>
@@ -10679,11 +10131,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
+      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10706,7 +10154,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -10731,11 +10179,7 @@
           <t>VS</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE02-0002</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>VSSTRESU</t>
@@ -10762,11 +10206,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10789,7 +10229,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -10814,11 +10254,7 @@
           <t>VS</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0018</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>VSSTRESU</t>
@@ -10845,11 +10281,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10872,7 +10304,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -10897,11 +10329,7 @@
           <t>VS</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0018</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>VSSTRESU</t>
@@ -10928,11 +10356,7 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>mmHg</t>
-        </is>
-      </c>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10955,7 +10379,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -11478,11 +10902,7 @@
           <t>IE</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>BI-1245.110-GBR_SITE01-0009</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>IETEST</t>
@@ -11509,11 +10929,7 @@
           <t>Inconsistent Test Name</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>Subject has participated in another clinical trial within 30 days</t>
-        </is>
-      </c>
+      <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11536,7 +10952,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -11561,11 +10977,7 @@
           <t>IE</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>BI-1245.110-GBR_SITE01-0009</t>
-        </is>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>IETESTCD</t>
